--- a/research/traditional_assets/database/data/tunisia/tunisia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0951</v>
+        <v>0.0636</v>
       </c>
       <c r="E2">
-        <v>-0.008539999999999999</v>
+        <v>-0.00336</v>
       </c>
       <c r="G2">
-        <v>0.1223021582733813</v>
+        <v>0.1639198218262806</v>
       </c>
       <c r="H2">
-        <v>0.1223021582733813</v>
+        <v>0.1639198218262806</v>
       </c>
       <c r="I2">
-        <v>0.1107913669064748</v>
+        <v>0.1612472160356347</v>
       </c>
       <c r="J2">
-        <v>0.1107913669064748</v>
+        <v>0.1231503463129298</v>
       </c>
       <c r="K2">
-        <v>5.32</v>
+        <v>5.56</v>
       </c>
       <c r="L2">
-        <v>0.1275779376498801</v>
+        <v>0.1238307349665924</v>
       </c>
       <c r="M2">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="N2">
-        <v>0.03568548387096774</v>
+        <v>0.05055679287305122</v>
       </c>
       <c r="O2">
-        <v>0.3327067669172932</v>
+        <v>0.408273381294964</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="Q2">
-        <v>0.03568548387096774</v>
+        <v>0.05055679287305122</v>
       </c>
       <c r="R2">
-        <v>0.3327067669172932</v>
+        <v>0.408273381294964</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="V2">
-        <v>0.07560483870967742</v>
+        <v>0.044543429844098</v>
       </c>
       <c r="W2">
-        <v>0.07218453188602443</v>
+        <v>0.07002518891687656</v>
       </c>
       <c r="X2">
-        <v>0.1795909741106859</v>
+        <v>0.245142017110848</v>
       </c>
       <c r="Y2">
-        <v>-0.1074064422246615</v>
+        <v>-0.1751168281939714</v>
       </c>
       <c r="Z2">
-        <v>0.5860857343640197</v>
+        <v>0.5935228023793786</v>
       </c>
       <c r="AA2">
-        <v>0.06493323963457484</v>
+        <v>0.07309253865764111</v>
       </c>
       <c r="AB2">
-        <v>0.1795909741106859</v>
+        <v>0.2450741957430655</v>
       </c>
       <c r="AC2">
-        <v>-0.1146577344761111</v>
+        <v>-0.1719816570854245</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="AG2">
-        <v>-3.75</v>
+        <v>-1.976</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.0005342355978986734</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.0003216123499142367</v>
       </c>
       <c r="AJ2">
-        <v>-0.08178844056706652</v>
+        <v>-0.04603485229708322</v>
       </c>
       <c r="AK2">
-        <v>-0.0495703899537343</v>
+        <v>-0.02720863626349416</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.003230148048452221</v>
+      </c>
+      <c r="AO2">
+        <v>7.029126213592233</v>
       </c>
       <c r="AP2">
-        <v>-0.78125</v>
+        <v>-0.2659488559892328</v>
+      </c>
+      <c r="AQ2">
+        <v>7.029126213592233</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0951</v>
+        <v>0.0636</v>
       </c>
       <c r="E3">
-        <v>-0.008539999999999999</v>
+        <v>-0.00336</v>
       </c>
       <c r="G3">
-        <v>0.1223021582733813</v>
+        <v>0.1639198218262806</v>
       </c>
       <c r="H3">
-        <v>0.1223021582733813</v>
+        <v>0.1639198218262806</v>
       </c>
       <c r="I3">
-        <v>0.1107913669064748</v>
+        <v>0.1612472160356347</v>
       </c>
       <c r="J3">
-        <v>0.1107913669064748</v>
+        <v>0.1231503463129298</v>
       </c>
       <c r="K3">
-        <v>5.32</v>
+        <v>5.56</v>
       </c>
       <c r="L3">
-        <v>0.1275779376498801</v>
+        <v>0.1238307349665924</v>
       </c>
       <c r="M3">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="N3">
-        <v>0.03568548387096774</v>
+        <v>0.05055679287305122</v>
       </c>
       <c r="O3">
-        <v>0.3327067669172932</v>
+        <v>0.408273381294964</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="Q3">
-        <v>0.03568548387096774</v>
+        <v>0.05055679287305122</v>
       </c>
       <c r="R3">
-        <v>0.3327067669172932</v>
+        <v>0.408273381294964</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>0.07560483870967742</v>
+        <v>0.044543429844098</v>
       </c>
       <c r="W3">
-        <v>0.07218453188602443</v>
+        <v>0.07002518891687656</v>
       </c>
       <c r="X3">
-        <v>0.1795909741106859</v>
+        <v>0.245142017110848</v>
       </c>
       <c r="Y3">
-        <v>-0.1074064422246615</v>
+        <v>-0.1751168281939714</v>
       </c>
       <c r="Z3">
-        <v>0.5860857343640197</v>
+        <v>0.5935228023793786</v>
       </c>
       <c r="AA3">
-        <v>0.06493323963457484</v>
+        <v>0.07309253865764111</v>
       </c>
       <c r="AB3">
-        <v>0.1795909741106859</v>
+        <v>0.2450741957430655</v>
       </c>
       <c r="AC3">
-        <v>-0.1146577344761111</v>
+        <v>-0.1719816570854245</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="AG3">
-        <v>-3.75</v>
+        <v>-1.976</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.0005342355978986734</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.0003216123499142367</v>
       </c>
       <c r="AJ3">
-        <v>-0.08178844056706652</v>
+        <v>-0.04603485229708322</v>
       </c>
       <c r="AK3">
-        <v>-0.0495703899537343</v>
+        <v>-0.02720863626349416</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.003230148048452221</v>
+      </c>
+      <c r="AO3">
+        <v>7.029126213592233</v>
       </c>
       <c r="AP3">
-        <v>-0.78125</v>
+        <v>-0.2659488559892328</v>
+      </c>
+      <c r="AQ3">
+        <v>7.029126213592233</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tunisia/tunisia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0636</v>
+        <v>0.135</v>
       </c>
       <c r="E2">
-        <v>-0.00336</v>
+        <v>0.0129</v>
       </c>
       <c r="G2">
-        <v>0.1639198218262806</v>
+        <v>0.1120401337792642</v>
       </c>
       <c r="H2">
-        <v>0.1639198218262806</v>
+        <v>0.1120401337792642</v>
       </c>
       <c r="I2">
-        <v>0.1612472160356347</v>
+        <v>0.09966555183946489</v>
       </c>
       <c r="J2">
-        <v>0.1231503463129298</v>
+        <v>0.06356800572904367</v>
       </c>
       <c r="K2">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="L2">
-        <v>0.1238307349665924</v>
+        <v>0.09381270903010035</v>
       </c>
       <c r="M2">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="N2">
-        <v>0.05055679287305122</v>
+        <v>0.05522388059701493</v>
       </c>
       <c r="O2">
-        <v>0.408273381294964</v>
+        <v>0.4616755793226381</v>
       </c>
       <c r="P2">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="Q2">
-        <v>0.05055679287305122</v>
+        <v>0.05522388059701493</v>
       </c>
       <c r="R2">
-        <v>0.408273381294964</v>
+        <v>0.4616755793226381</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>3.54</v>
       </c>
       <c r="V2">
-        <v>0.044543429844098</v>
+        <v>0.07547974413646055</v>
       </c>
       <c r="W2">
-        <v>0.07002518891687656</v>
+        <v>0.075201072386059</v>
       </c>
       <c r="X2">
-        <v>0.245142017110848</v>
+        <v>0.2289980370426353</v>
       </c>
       <c r="Y2">
-        <v>-0.1751168281939714</v>
+        <v>-0.1537969646565763</v>
       </c>
       <c r="Z2">
-        <v>0.5935228023793786</v>
+        <v>0.8234192553425865</v>
       </c>
       <c r="AA2">
-        <v>0.07309253865764111</v>
+        <v>0.05234311994102241</v>
       </c>
       <c r="AB2">
-        <v>0.2450741957430655</v>
+        <v>0.2289980370426353</v>
       </c>
       <c r="AC2">
-        <v>-0.1719816570854245</v>
+        <v>-0.1766549171016129</v>
       </c>
       <c r="AD2">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.976</v>
+        <v>-3.54</v>
       </c>
       <c r="AH2">
-        <v>0.0005342355978986734</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.0003216123499142367</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.04603485229708322</v>
+        <v>-0.08164206642066421</v>
       </c>
       <c r="AK2">
-        <v>-0.02720863626349416</v>
+        <v>-0.04805864784143361</v>
       </c>
       <c r="AL2">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.003230148048452221</v>
-      </c>
-      <c r="AO2">
-        <v>7.029126213592233</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.2659488559892328</v>
-      </c>
-      <c r="AQ2">
-        <v>7.029126213592233</v>
+        <v>-0.5746753246753247</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0636</v>
+        <v>0.135</v>
       </c>
       <c r="E3">
-        <v>-0.00336</v>
+        <v>0.0129</v>
       </c>
       <c r="G3">
-        <v>0.1639198218262806</v>
+        <v>0.1120401337792642</v>
       </c>
       <c r="H3">
-        <v>0.1639198218262806</v>
+        <v>0.1120401337792642</v>
       </c>
       <c r="I3">
-        <v>0.1612472160356347</v>
+        <v>0.09966555183946489</v>
       </c>
       <c r="J3">
-        <v>0.1231503463129298</v>
+        <v>0.06356800572904367</v>
       </c>
       <c r="K3">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="L3">
-        <v>0.1238307349665924</v>
+        <v>0.09381270903010035</v>
       </c>
       <c r="M3">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="N3">
-        <v>0.05055679287305122</v>
+        <v>0.05522388059701493</v>
       </c>
       <c r="O3">
-        <v>0.408273381294964</v>
+        <v>0.4616755793226381</v>
       </c>
       <c r="P3">
-        <v>2.27</v>
+        <v>2.59</v>
       </c>
       <c r="Q3">
-        <v>0.05055679287305122</v>
+        <v>0.05522388059701493</v>
       </c>
       <c r="R3">
-        <v>0.408273381294964</v>
+        <v>0.4616755793226381</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>3.54</v>
       </c>
       <c r="V3">
-        <v>0.044543429844098</v>
+        <v>0.07547974413646055</v>
       </c>
       <c r="W3">
-        <v>0.07002518891687656</v>
+        <v>0.075201072386059</v>
       </c>
       <c r="X3">
-        <v>0.245142017110848</v>
+        <v>0.2289980370426353</v>
       </c>
       <c r="Y3">
-        <v>-0.1751168281939714</v>
+        <v>-0.1537969646565763</v>
       </c>
       <c r="Z3">
-        <v>0.5935228023793786</v>
+        <v>0.8234192553425865</v>
       </c>
       <c r="AA3">
-        <v>0.07309253865764111</v>
+        <v>0.05234311994102241</v>
       </c>
       <c r="AB3">
-        <v>0.2450741957430655</v>
+        <v>0.2289980370426353</v>
       </c>
       <c r="AC3">
-        <v>-0.1719816570854245</v>
+        <v>-0.1766549171016129</v>
       </c>
       <c r="AD3">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.976</v>
+        <v>-3.54</v>
       </c>
       <c r="AH3">
-        <v>0.0005342355978986734</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.0003216123499142367</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.04603485229708322</v>
+        <v>-0.08164206642066421</v>
       </c>
       <c r="AK3">
-        <v>-0.02720863626349416</v>
+        <v>-0.04805864784143361</v>
       </c>
       <c r="AL3">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.003230148048452221</v>
-      </c>
-      <c r="AO3">
-        <v>7.029126213592233</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.2659488559892328</v>
-      </c>
-      <c r="AQ3">
-        <v>7.029126213592233</v>
+        <v>-0.5746753246753247</v>
       </c>
     </row>
   </sheetData>
